--- a/research/traditional_assets/database/data/singapore/singapore_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0659</v>
+        <v>-0.07965</v>
       </c>
       <c r="E2">
-        <v>0.12915</v>
-      </c>
-      <c r="F2">
-        <v>0.324</v>
+        <v>-0.065</v>
       </c>
       <c r="G2">
-        <v>0.1476857078347256</v>
+        <v>0.2851721018394865</v>
       </c>
       <c r="H2">
-        <v>0.1272747798600135</v>
+        <v>0.2625985439193556</v>
       </c>
       <c r="I2">
-        <v>0.2142560397380898</v>
+        <v>0.09951751173911171</v>
       </c>
       <c r="J2">
-        <v>0.2012009520933093</v>
+        <v>0.09465259724608453</v>
       </c>
       <c r="K2">
-        <v>28.519</v>
+        <v>53.555</v>
       </c>
       <c r="L2">
-        <v>0.1287830209979679</v>
+        <v>0.2307112393917202</v>
       </c>
       <c r="M2">
-        <v>10.312</v>
+        <v>15.93</v>
       </c>
       <c r="N2">
-        <v>0.005091810096024467</v>
+        <v>0.005303494380226922</v>
       </c>
       <c r="O2">
-        <v>0.3615835057330201</v>
+        <v>0.2974512183736346</v>
       </c>
       <c r="P2">
-        <v>10.312</v>
+        <v>14.26</v>
       </c>
       <c r="Q2">
-        <v>0.005091810096024467</v>
+        <v>0.004747509721408406</v>
       </c>
       <c r="R2">
-        <v>0.3615835057330201</v>
+        <v>0.2662683222855009</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1048336472065286</v>
       </c>
       <c r="U2">
-        <v>70.396</v>
+        <v>151.196</v>
       </c>
       <c r="V2">
-        <v>0.03475980057406308</v>
+        <v>0.05033692004474512</v>
       </c>
       <c r="W2">
-        <v>-0.2470046082949309</v>
+        <v>-0.01601648351648351</v>
       </c>
       <c r="X2">
-        <v>0.04400544573928451</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y2">
-        <v>-0.2910100540342154</v>
+        <v>-0.08847070255718836</v>
       </c>
       <c r="Z2">
-        <v>0.5934467613001428</v>
+        <v>0.6292644710768222</v>
       </c>
       <c r="AA2">
-        <v>0.01827095160295433</v>
+        <v>-1.008636363636364</v>
       </c>
       <c r="AB2">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC2">
-        <v>-0.02524299885516503</v>
+        <v>-1.081090582677068</v>
       </c>
       <c r="AD2">
-        <v>115.958</v>
+        <v>91.21799999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>115.958</v>
+        <v>91.21799999999999</v>
       </c>
       <c r="AG2">
-        <v>45.562</v>
+        <v>-59.97800000000001</v>
       </c>
       <c r="AH2">
-        <v>0.05415634715770016</v>
+        <v>0.02947366924531923</v>
       </c>
       <c r="AI2">
-        <v>0.2710983929264449</v>
+        <v>0.1954808265149989</v>
       </c>
       <c r="AJ2">
-        <v>0.02200239040938779</v>
+        <v>-0.02037502437407048</v>
       </c>
       <c r="AK2">
-        <v>0.1275039318516362</v>
+        <v>-0.1901419613363007</v>
       </c>
       <c r="AL2">
-        <v>4.127</v>
+        <v>3.554</v>
       </c>
       <c r="AM2">
-        <v>3.149999999999999</v>
+        <v>-3.874999999999999</v>
       </c>
       <c r="AN2">
-        <v>1.914667371167214</v>
+        <v>2.003338238200865</v>
       </c>
       <c r="AO2">
-        <v>11.49672885873516</v>
+        <v>6.499999999999999</v>
       </c>
       <c r="AP2">
-        <v>0.7523075144890444</v>
+        <v>-1.317242439549338</v>
       </c>
       <c r="AQ2">
-        <v>15.06253968253968</v>
+        <v>-5.961548387096776</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZACD Group Ltd. (SEHK:8313)</t>
+          <t>iFAST Corporation Ltd. (SGX:AIY)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,98 +721,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.178</v>
+      </c>
+      <c r="E3">
+        <v>0.118</v>
+      </c>
       <c r="G3">
-        <v>-1</v>
+        <v>0.2298527443105756</v>
       </c>
       <c r="H3">
-        <v>-1</v>
+        <v>0.1947791164658635</v>
       </c>
       <c r="I3">
-        <v>2.859934853420195</v>
+        <v>0.1044176706827309</v>
       </c>
       <c r="J3">
-        <v>2.859934853420195</v>
+        <v>0.07300157150340492</v>
       </c>
       <c r="K3">
-        <v>-3.63</v>
+        <v>8.59</v>
       </c>
       <c r="L3">
-        <v>-1.182410423452769</v>
+        <v>0.05749665327978581</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>11.32</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.008869388074904019</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.317811408614668</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>9.65</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.007560918279401395</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.123399301513388</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.67</v>
+      </c>
+      <c r="T3">
+        <v>0.1475265017667844</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.07396380161404059</v>
+      </c>
+      <c r="W3">
+        <v>0.09306608884073674</v>
       </c>
       <c r="X3">
-        <v>0.04894495259023699</v>
+        <v>0.07266125985952787</v>
+      </c>
+      <c r="Y3">
+        <v>0.02040482898120886</v>
+      </c>
+      <c r="Z3">
+        <v>1.90561224489796</v>
+      </c>
+      <c r="AA3">
+        <v>0.1391126885536824</v>
       </c>
       <c r="AB3">
-        <v>0.04443679897722341</v>
+        <v>0.07246252407814478</v>
+      </c>
+      <c r="AC3">
+        <v>0.06665016447553758</v>
       </c>
       <c r="AD3">
-        <v>2.23</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.23</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AG3">
-        <v>2.23</v>
+        <v>-84.94</v>
       </c>
       <c r="AH3">
-        <v>0.1751767478397486</v>
+        <v>0.007357516177202589</v>
       </c>
       <c r="AI3">
-        <v>0.1685563114134543</v>
+        <v>0.05562742561448901</v>
       </c>
       <c r="AJ3">
-        <v>0.1751767478397486</v>
+        <v>-0.07129666935267258</v>
       </c>
       <c r="AK3">
-        <v>0.1685563114134543</v>
+        <v>-1.122653978324081</v>
       </c>
       <c r="AL3">
-        <v>0.06900000000000001</v>
+        <v>0.664</v>
       </c>
       <c r="AM3">
-        <v>0.06900000000000001</v>
+        <v>-0.1739999999999999</v>
       </c>
       <c r="AN3">
-        <v>0.2488839285714285</v>
+        <v>0.5058823529411766</v>
       </c>
       <c r="AO3">
-        <v>127.2463768115942</v>
+        <v>23.49397590361446</v>
       </c>
       <c r="AP3">
-        <v>0.2488839285714285</v>
+        <v>-4.542245989304813</v>
       </c>
       <c r="AQ3">
-        <v>127.2463768115942</v>
+        <v>-89.65517241379314</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iFAST Corporation Ltd. (SGX:AIY)</t>
+          <t>Forise International Limited (SGX:8A1)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -834,125 +855,104 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.213</v>
-      </c>
-      <c r="E4">
-        <v>0.334</v>
-      </c>
-      <c r="F4">
-        <v>0.324</v>
-      </c>
       <c r="G4">
-        <v>0.1594559585492228</v>
+        <v>0.07565217391304348</v>
       </c>
       <c r="H4">
-        <v>0.1301813471502591</v>
+        <v>0.07565217391304348</v>
       </c>
       <c r="I4">
-        <v>0.1709844559585492</v>
+        <v>0.1808695652173913</v>
       </c>
       <c r="J4">
-        <v>0.1436789534860813</v>
+        <v>0.1400538668718738</v>
       </c>
       <c r="K4">
-        <v>22.3</v>
+        <v>-0.031</v>
       </c>
       <c r="L4">
-        <v>0.1444300518134715</v>
+        <v>-0.02695652173913044</v>
       </c>
       <c r="M4">
-        <v>7.92</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.00458970792767733</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.3551569506726457</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>7.92</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.00458970792767733</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.3551569506726457</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>26.5</v>
+        <v>1.27</v>
       </c>
       <c r="V4">
-        <v>0.01535697728326379</v>
+        <v>0.2360594795539034</v>
       </c>
       <c r="W4">
-        <v>0.3029891304347826</v>
+        <v>-0.01703296703296703</v>
       </c>
       <c r="X4">
-        <v>0.04404734266036772</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y4">
-        <v>0.258941787774415</v>
+        <v>-0.08948718607367188</v>
       </c>
       <c r="Z4">
-        <v>2.301043219076006</v>
+        <v>0.7958477508650518</v>
       </c>
       <c r="AA4">
-        <v>0.3306114816430842</v>
+        <v>0.1114615549499341</v>
       </c>
       <c r="AB4">
-        <v>0.04389629578609216</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC4">
-        <v>0.286715185856992</v>
+        <v>0.03900733590922929</v>
       </c>
       <c r="AD4">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-13.9</v>
+        <v>-1.27</v>
       </c>
       <c r="AH4">
-        <v>0.007248878149810149</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.1208053691275168</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.00812058187766548</v>
+        <v>-0.3090024330900244</v>
       </c>
       <c r="AK4">
-        <v>-0.1786632390745501</v>
+        <v>-1.530120481927711</v>
       </c>
       <c r="AL4">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.45</v>
-      </c>
-      <c r="AN4">
-        <v>0.4329896907216494</v>
-      </c>
-      <c r="AO4">
-        <v>56.89655172413792</v>
-      </c>
-      <c r="AP4">
-        <v>-0.4776632302405498</v>
+        <v>-0.004</v>
       </c>
       <c r="AQ4">
-        <v>-58.66666666666666</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TIH Limited (SGX:T55)</t>
+          <t>Uni-Asia Group Limited (SGX:CHJ)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,46 +972,43 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0443</v>
-      </c>
-      <c r="E5">
-        <v>-0.0757</v>
+        <v>-0.0493</v>
       </c>
       <c r="G5">
-        <v>-0.4526315789473684</v>
+        <v>0.2548476454293628</v>
       </c>
       <c r="H5">
-        <v>-0.4526315789473684</v>
+        <v>0.2548476454293628</v>
       </c>
       <c r="I5">
-        <v>0.6728070175438596</v>
+        <v>0.2202216066481995</v>
       </c>
       <c r="J5">
-        <v>0.666166324903167</v>
+        <v>0.2113665420452124</v>
       </c>
       <c r="K5">
-        <v>7.62</v>
+        <v>27.4</v>
       </c>
       <c r="L5">
-        <v>0.6684210526315789</v>
+        <v>0.3795013850415512</v>
       </c>
       <c r="M5">
-        <v>1.8</v>
+        <v>2.87</v>
       </c>
       <c r="N5">
-        <v>0.04379562043795621</v>
+        <v>0.06119402985074628</v>
       </c>
       <c r="O5">
-        <v>0.2362204724409449</v>
+        <v>0.1047445255474453</v>
       </c>
       <c r="P5">
-        <v>1.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q5">
-        <v>0.04379562043795621</v>
+        <v>0.06119402985074628</v>
       </c>
       <c r="R5">
-        <v>0.2362204724409449</v>
+        <v>0.1047445255474453</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1020,73 +1017,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>10.7</v>
+        <v>45</v>
       </c>
       <c r="V5">
-        <v>0.2603406326034063</v>
+        <v>0.9594882729211087</v>
       </c>
       <c r="W5">
-        <v>0.08975265017667844</v>
+        <v>0.2240392477514309</v>
       </c>
       <c r="X5">
-        <v>0.04400544573928451</v>
+        <v>0.1195651026799244</v>
       </c>
       <c r="Y5">
-        <v>0.04574720443739393</v>
+        <v>0.1044741450715065</v>
       </c>
       <c r="Z5">
-        <v>0.1442471941390087</v>
+        <v>0.3782084861183866</v>
       </c>
       <c r="AA5">
-        <v>0.0960926231971771</v>
+        <v>0.0799406198829981</v>
       </c>
       <c r="AB5">
-        <v>0.04386957603201616</v>
+        <v>0.07316284377530519</v>
       </c>
       <c r="AC5">
-        <v>0.05222304716516094</v>
+        <v>0.006777776107692909</v>
       </c>
       <c r="AD5">
-        <v>0.228</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.228</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AG5">
-        <v>-10.472</v>
+        <v>34.09999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.005516840882694541</v>
+        <v>0.6277777777777778</v>
       </c>
       <c r="AI5">
-        <v>0.002422233554309026</v>
+        <v>0.3566275924256087</v>
       </c>
       <c r="AJ5">
-        <v>-0.3419093639806713</v>
+        <v>0.4209876543209876</v>
       </c>
       <c r="AK5">
-        <v>-0.1255214076808745</v>
+        <v>0.1928733031674208</v>
       </c>
       <c r="AL5">
-        <v>0.004</v>
+        <v>2.52</v>
       </c>
       <c r="AM5">
-        <v>-0.024</v>
+        <v>2.52</v>
       </c>
       <c r="AN5">
-        <v>0.02964889466840052</v>
+        <v>3.08984375</v>
       </c>
       <c r="AO5">
-        <v>1917.5</v>
+        <v>6.309523809523809</v>
       </c>
       <c r="AP5">
-        <v>-1.361768530559168</v>
+        <v>1.33203125</v>
       </c>
       <c r="AQ5">
-        <v>-319.5833333333333</v>
+        <v>6.309523809523809</v>
       </c>
     </row>
     <row r="6">
@@ -1097,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Uni-Asia Group Limited (SGX:CHJ)</t>
+          <t>TIH Limited (SGX:T55)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1106,43 +1103,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.08749999999999999</v>
+        <v>-0.11</v>
+      </c>
+      <c r="E6">
+        <v>-0.248</v>
       </c>
       <c r="G6">
-        <v>0.3215686274509804</v>
+        <v>1.462633451957295</v>
       </c>
       <c r="H6">
-        <v>0.3215686274509804</v>
+        <v>1.462633451957295</v>
       </c>
       <c r="I6">
-        <v>0.1086274509803922</v>
+        <v>0.3380782918149466</v>
       </c>
       <c r="J6">
-        <v>0.08071461561069825</v>
+        <v>0.2983043751308352</v>
       </c>
       <c r="K6">
-        <v>3.27</v>
+        <v>1.5</v>
       </c>
       <c r="L6">
-        <v>0.06411764705882353</v>
+        <v>0.2669039145907473</v>
       </c>
       <c r="M6">
-        <v>0.592</v>
+        <v>1.74</v>
       </c>
       <c r="N6">
-        <v>0.008256624825662482</v>
+        <v>0.04317617866004963</v>
       </c>
       <c r="O6">
-        <v>0.181039755351682</v>
+        <v>1.16</v>
       </c>
       <c r="P6">
-        <v>0.592</v>
+        <v>1.74</v>
       </c>
       <c r="Q6">
-        <v>0.008256624825662482</v>
+        <v>0.04317617866004963</v>
       </c>
       <c r="R6">
-        <v>0.181039755351682</v>
+        <v>1.16</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1151,73 +1151,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>32.3</v>
+        <v>7.29</v>
       </c>
       <c r="V6">
-        <v>0.4504881450488145</v>
+        <v>0.180893300248139</v>
       </c>
       <c r="W6">
-        <v>0.02713692946058091</v>
+        <v>0.01597444089456869</v>
       </c>
       <c r="X6">
-        <v>0.07748034796553199</v>
+        <v>0.07252630420665011</v>
       </c>
       <c r="Y6">
-        <v>-0.05034341850495108</v>
+        <v>-0.05655186331208142</v>
       </c>
       <c r="Z6">
-        <v>0.2263648468708389</v>
+        <v>0.06736347509229515</v>
       </c>
       <c r="AA6">
-        <v>0.01827095160295433</v>
+        <v>0.02009481934404869</v>
       </c>
       <c r="AB6">
-        <v>0.04351395045811936</v>
+        <v>0.07244067407999208</v>
       </c>
       <c r="AC6">
-        <v>-0.02524299885516503</v>
+        <v>-0.05234585473594339</v>
       </c>
       <c r="AD6">
-        <v>100.9</v>
+        <v>0.104</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>100.9</v>
+        <v>0.104</v>
       </c>
       <c r="AG6">
-        <v>68.60000000000001</v>
+        <v>-7.186</v>
       </c>
       <c r="AH6">
-        <v>0.5845886442641947</v>
+        <v>0.002574002574002574</v>
       </c>
       <c r="AI6">
-        <v>0.4512522361359571</v>
+        <v>0.001147852191956205</v>
       </c>
       <c r="AJ6">
-        <v>0.488952245188881</v>
+        <v>-0.2170079120613638</v>
       </c>
       <c r="AK6">
-        <v>0.3585990590695243</v>
+        <v>-0.08625201046642822</v>
       </c>
       <c r="AL6">
-        <v>3.59</v>
+        <v>0.308</v>
       </c>
       <c r="AM6">
-        <v>3.59</v>
+        <v>0.308</v>
       </c>
       <c r="AN6">
-        <v>6.726666666666667</v>
+        <v>0.05445026178010471</v>
       </c>
       <c r="AO6">
-        <v>1.543175487465181</v>
+        <v>6.168831168831169</v>
       </c>
       <c r="AP6">
-        <v>4.573333333333334</v>
+        <v>-3.762303664921466</v>
       </c>
       <c r="AQ6">
-        <v>1.543175487465181</v>
+        <v>6.168831168831169</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Forise International Limited (SGX:8A1)</t>
+          <t>HHG Capital Corporation (NasdaqCM:HHGC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1236,26 +1236,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.233</v>
-      </c>
-      <c r="G7">
-        <v>-0.05379746835443038</v>
-      </c>
-      <c r="H7">
-        <v>-0.05379746835443038</v>
-      </c>
-      <c r="I7">
-        <v>-0.1183544303797468</v>
-      </c>
-      <c r="J7">
-        <v>-0.1183544303797468</v>
-      </c>
       <c r="K7">
-        <v>-0.536</v>
-      </c>
-      <c r="L7">
-        <v>-0.339240506329114</v>
+        <v>-0.162</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1279,70 +1261,64 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.375</v>
+        <v>0.457</v>
       </c>
       <c r="V7">
-        <v>0.1569037656903766</v>
+        <v>0.008908382066276805</v>
       </c>
       <c r="W7">
-        <v>-0.2470046082949309</v>
+        <v>-0.015</v>
       </c>
       <c r="X7">
-        <v>0.04387296409148227</v>
+        <v>0.07251955939580143</v>
       </c>
       <c r="Y7">
-        <v>-0.2908775723864132</v>
+        <v>-0.08751955939580143</v>
       </c>
       <c r="Z7">
-        <v>0.9640024405125076</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>-0.1140939597315436</v>
+        <v>-0.04704112337011033</v>
       </c>
       <c r="AB7">
-        <v>0.04387296409148227</v>
+        <v>0.07246421386628965</v>
       </c>
       <c r="AC7">
-        <v>-0.1579669238230259</v>
+        <v>-0.1195053372364</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG7">
-        <v>-0.375</v>
+        <v>-0.337</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.002333722287047842</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>-0.103448275862069</v>
       </c>
       <c r="AJ7">
-        <v>-0.1861042183622829</v>
+        <v>-0.006612640543139142</v>
       </c>
       <c r="AK7">
-        <v>-0.2427184466019418</v>
+        <v>0.2084106369820656</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.007</v>
-      </c>
-      <c r="AN7">
-        <v>-0</v>
-      </c>
-      <c r="AP7">
-        <v>2.005347593582888</v>
+        <v>-0.307</v>
       </c>
       <c r="AQ7">
-        <v>26.71428571428572</v>
+        <v>1.527687296416938</v>
       </c>
     </row>
     <row r="8">
@@ -1353,7 +1329,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Compass Venture Inc. (TSXV:CVI.P)</t>
+          <t>Nova Vision Acquisition Corporation (NasdaqCM:NOVV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1362,7 +1338,7 @@
         </is>
       </c>
       <c r="K8">
-        <v>-0.154</v>
+        <v>-0.446</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1386,61 +1362,64 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.405</v>
+        <v>0.227</v>
       </c>
       <c r="V8">
-        <v>0.5601659751037344</v>
+        <v>0.0060857908847185</v>
       </c>
       <c r="W8">
-        <v>-1.673913043478261</v>
+        <v>-0.0892</v>
       </c>
       <c r="X8">
-        <v>0.04387296409148227</v>
+        <v>0.07289156148181505</v>
       </c>
       <c r="Y8">
-        <v>-1.717786007569743</v>
+        <v>-0.1620915614818151</v>
       </c>
       <c r="Z8">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>-5.875000000000001</v>
+        <v>-0.1894262683736368</v>
       </c>
       <c r="AB8">
-        <v>0.04387296409148227</v>
+        <v>0.07237309944228966</v>
       </c>
       <c r="AC8">
-        <v>-5.918872964091483</v>
+        <v>-0.2617993678159264</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="AG8">
-        <v>-0.405</v>
+        <v>0.357</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.01541547883011297</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>-1.280701754385965</v>
       </c>
       <c r="AJ8">
-        <v>-1.273584905660378</v>
+        <v>0.00948030910587673</v>
       </c>
       <c r="AK8">
-        <v>21.31578947368419</v>
+        <v>-0.5226939970717422</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>-0.353</v>
+      </c>
+      <c r="AQ8">
+        <v>2.263456090651558</v>
       </c>
     </row>
     <row r="9">
@@ -1451,7 +1430,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vickers Vantage Corp. I (NasdaqCM:VCKA)</t>
+          <t>A SPAC II Acquisition Corporation (NasdaqGM:ASCB)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1460,7 +1439,7 @@
         </is>
       </c>
       <c r="K9">
-        <v>-0.351</v>
+        <v>-0.006</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1484,31 +1463,31 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.116</v>
+        <v>1.12</v>
       </c>
       <c r="V9">
-        <v>0.0006697459584295613</v>
+        <v>0.004327666151468315</v>
       </c>
       <c r="W9">
-        <v>-18.47368421052632</v>
+        <v>-0.2727272727272728</v>
       </c>
       <c r="X9">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y9">
-        <v>-18.5175571746178</v>
+        <v>-0.3451814917679776</v>
       </c>
       <c r="Z9">
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>-9.461538461538463</v>
+        <v>-0.24</v>
       </c>
       <c r="AB9">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC9">
-        <v>-9.505411425629946</v>
+        <v>-0.3124542190407049</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -1520,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>-0.116</v>
+        <v>-1.12</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1529,19 +1508,717 @@
         <v>-0</v>
       </c>
       <c r="AJ9">
-        <v>-0.0006701948187007466</v>
+        <v>-0.004346476249611922</v>
       </c>
       <c r="AK9">
-        <v>0.0116629800924995</v>
+        <v>0.163265306122449</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-0.028</v>
-      </c>
-      <c r="AQ9">
-        <v>21.96428571428571</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A SPAC I Acquisition Corp. (NasdaqCM:ASCA)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K10">
+        <v>0.025</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="V10">
+        <v>0.000992108229988726</v>
+      </c>
+      <c r="W10">
+        <v>1.086956521739131</v>
+      </c>
+      <c r="X10">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y10">
+        <v>1.014502302698426</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>-1.777272727272727</v>
+      </c>
+      <c r="AB10">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AC10">
+        <v>-1.849726946313432</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>-0.08799999999999999</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.0009930934862095425</v>
+      </c>
+      <c r="AK10">
+        <v>-0.02339181286549707</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>-0.416</v>
+      </c>
+      <c r="AQ10">
+        <v>0.9399038461538463</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chenghe Acquisition Co. (NasdaqGM:CHEA)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>0.206</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>-0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>-0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0.672</v>
+      </c>
+      <c r="V11">
+        <v>0.004537474679270763</v>
+      </c>
+      <c r="W11">
+        <v>12.875</v>
+      </c>
+      <c r="X11">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y11">
+        <v>12.80254578095929</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>-2.842105263157894</v>
+      </c>
+      <c r="AB11">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AC11">
+        <v>-2.914559482198599</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>-0.672</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>-0</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.004558157202159699</v>
+      </c>
+      <c r="AK11">
+        <v>0.1674975074775673</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-0.655</v>
+      </c>
+      <c r="AQ11">
+        <v>0.6595419847328244</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fat Projects Acquisition Corp (NasdaqGM:FATP)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K12">
+        <v>-1.21</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0.244</v>
+      </c>
+      <c r="V12">
+        <v>0.001660993873383254</v>
+      </c>
+      <c r="W12">
+        <v>48.4</v>
+      </c>
+      <c r="X12">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y12">
+        <v>48.32754578095929</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>-17.71929824561403</v>
+      </c>
+      <c r="AB12">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AC12">
+        <v>-17.79175246465474</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>-0.244</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>-0</v>
+      </c>
+      <c r="AJ12">
+        <v>-0.00166375736417194</v>
+      </c>
+      <c r="AK12">
+        <v>0.04847040127135479</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-0.8090000000000001</v>
+      </c>
+      <c r="AQ12">
+        <v>2.496909765142151</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RF Acquisition Corp. (NasdaqGM:RFAC)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K13">
+        <v>-0.155</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0.285</v>
+      </c>
+      <c r="V13">
+        <v>0.001933514246947082</v>
+      </c>
+      <c r="W13">
+        <v>-8.157894736842106</v>
+      </c>
+      <c r="X13">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y13">
+        <v>-8.23034895588281</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>-38.78947368421053</v>
+      </c>
+      <c r="AB13">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AC13">
+        <v>-38.86192790325124</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>-0.285</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>-0.001937259966692723</v>
+      </c>
+      <c r="AK13">
+        <v>2.209302325581396</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-0.697</v>
+      </c>
+      <c r="AQ13">
+        <v>1.057388809182209</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Catcha Investment Corp (NYSE:CHAA)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K14">
+        <v>10.1</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0.076</v>
+      </c>
+      <c r="V14">
+        <v>0.000200845665961945</v>
+      </c>
+      <c r="W14">
+        <v>-0.5179487179487179</v>
+      </c>
+      <c r="X14">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y14">
+        <v>-0.5904029369894227</v>
+      </c>
+      <c r="AB14">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>-0.076</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>-0</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.0002008860130470179</v>
+      </c>
+      <c r="AK14">
+        <v>0.00662251655629139</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-1.63</v>
+      </c>
+      <c r="AQ14">
+        <v>0.7914110429447854</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>L Catterton Asia Acquisition Corp (NasdaqCM:LCAA)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K15">
+        <v>7.96</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0.067</v>
+      </c>
+      <c r="V15">
+        <v>0.0001852363837434338</v>
+      </c>
+      <c r="W15">
+        <v>-0.4124352331606218</v>
+      </c>
+      <c r="X15">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y15">
+        <v>-0.4848894522013266</v>
+      </c>
+      <c r="AB15">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>-0.067</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>-0</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.0001852707026184004</v>
+      </c>
+      <c r="AK15">
+        <v>0.005088478772689299</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>-1.72</v>
+      </c>
+      <c r="AQ15">
+        <v>2.13953488372093</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ZACD Group Ltd. (SEHK:8313)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>-0.18</v>
+      </c>
+      <c r="G16">
+        <v>1.36968085106383</v>
+      </c>
+      <c r="H16">
+        <v>1.36968085106383</v>
+      </c>
+      <c r="I16">
+        <v>-0.1816489361702128</v>
+      </c>
+      <c r="J16">
+        <v>-0.1816489361702128</v>
+      </c>
+      <c r="K16">
+        <v>-0.216</v>
+      </c>
+      <c r="L16">
+        <v>-0.0574468085106383</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0.07564409887632229</v>
+      </c>
+      <c r="AB16">
+        <v>0.07289317461476016</v>
+      </c>
+      <c r="AD16">
+        <v>1.85</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1.85</v>
+      </c>
+      <c r="AG16">
+        <v>1.85</v>
+      </c>
+      <c r="AH16">
+        <v>0.1024930747922438</v>
+      </c>
+      <c r="AI16">
+        <v>0.1024930747922438</v>
+      </c>
+      <c r="AJ16">
+        <v>0.1024930747922438</v>
+      </c>
+      <c r="AK16">
+        <v>0.1024930747922438</v>
+      </c>
+      <c r="AL16">
+        <v>0.062</v>
+      </c>
+      <c r="AM16">
+        <v>0.062</v>
+      </c>
+      <c r="AN16">
+        <v>-2.732644017725258</v>
+      </c>
+      <c r="AO16">
+        <v>-11.01612903225807</v>
+      </c>
+      <c r="AP16">
+        <v>-2.732644017725258</v>
+      </c>
+      <c r="AQ16">
+        <v>-11.01612903225807</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/singapore/singapore_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AQ21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.07965</v>
+        <v>-0.113</v>
       </c>
       <c r="E2">
-        <v>-0.065</v>
+        <v>0.1455</v>
+      </c>
+      <c r="F2">
+        <v>0.4384999999999999</v>
       </c>
       <c r="G2">
-        <v>0.2851721018394865</v>
+        <v>0.5494685097791693</v>
       </c>
       <c r="H2">
-        <v>0.2625985439193556</v>
+        <v>0.5365313313798681</v>
       </c>
       <c r="I2">
-        <v>0.09951751173911171</v>
+        <v>0.4477016130717753</v>
       </c>
       <c r="J2">
-        <v>0.09465259724608453</v>
+        <v>0.4070914210032623</v>
       </c>
       <c r="K2">
-        <v>53.555</v>
+        <v>179.186</v>
       </c>
       <c r="L2">
-        <v>0.2307112393917202</v>
+        <v>0.3745010094761174</v>
       </c>
       <c r="M2">
-        <v>15.93</v>
+        <v>993.3317</v>
       </c>
       <c r="N2">
-        <v>0.005303494380226922</v>
+        <v>0.2320418470249928</v>
       </c>
       <c r="O2">
-        <v>0.2974512183736346</v>
+        <v>5.543578739410444</v>
       </c>
       <c r="P2">
-        <v>14.26</v>
+        <v>67.31270000000001</v>
       </c>
       <c r="Q2">
-        <v>0.004747509721408406</v>
+        <v>0.01572421703267824</v>
       </c>
       <c r="R2">
-        <v>0.2662683222855009</v>
+        <v>0.3756582545511368</v>
       </c>
       <c r="S2">
-        <v>1.67</v>
+        <v>926.019</v>
       </c>
       <c r="T2">
-        <v>0.1048336472065286</v>
+        <v>0.9322354254877803</v>
       </c>
       <c r="U2">
-        <v>151.196</v>
+        <v>606.5309999999999</v>
       </c>
       <c r="V2">
-        <v>0.05033692004474512</v>
+        <v>0.1416853740980137</v>
       </c>
       <c r="W2">
-        <v>-0.01601648351648351</v>
+        <v>-0.2086538461538461</v>
       </c>
       <c r="X2">
-        <v>0.07245421904070486</v>
+        <v>0.06232407339310446</v>
       </c>
       <c r="Y2">
-        <v>-0.08847070255718836</v>
+        <v>-0.2709779195469506</v>
       </c>
       <c r="Z2">
-        <v>0.6292644710768222</v>
-      </c>
-      <c r="AA2">
-        <v>-1.008636363636364</v>
+        <v>0.1567804926960002</v>
       </c>
       <c r="AB2">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AC2">
-        <v>-1.081090582677068</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD2">
-        <v>91.21799999999999</v>
+        <v>106.028</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>91.21799999999999</v>
+        <v>106.028</v>
       </c>
       <c r="AG2">
-        <v>-59.97800000000001</v>
+        <v>-500.5029999999999</v>
       </c>
       <c r="AH2">
-        <v>0.02947366924531923</v>
+        <v>0.02416946251736437</v>
       </c>
       <c r="AI2">
-        <v>0.1954808265149989</v>
+        <v>0.03199635941374008</v>
       </c>
       <c r="AJ2">
-        <v>-0.02037502437407048</v>
+        <v>-0.1323967476887581</v>
       </c>
       <c r="AK2">
-        <v>-0.1901419613363007</v>
+        <v>-0.1848770381139922</v>
       </c>
       <c r="AL2">
-        <v>3.554</v>
+        <v>7.555</v>
       </c>
       <c r="AM2">
-        <v>-3.874999999999999</v>
+        <v>-51.455</v>
       </c>
       <c r="AN2">
-        <v>2.003338238200865</v>
+        <v>0.3972425162039639</v>
       </c>
       <c r="AO2">
-        <v>6.499999999999999</v>
+        <v>28.35340833884845</v>
       </c>
       <c r="AP2">
-        <v>-1.317242439549338</v>
+        <v>-1.875175152673185</v>
       </c>
       <c r="AQ2">
-        <v>-5.961548387096776</v>
+        <v>-4.163055096686425</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iFAST Corporation Ltd. (SGX:AIY)</t>
+          <t>ZACD Group Ltd. (SEHK:8313)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +719,100 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.178</v>
-      </c>
-      <c r="E3">
-        <v>0.118</v>
+        <v>-0.123</v>
       </c>
       <c r="G3">
-        <v>0.2298527443105756</v>
+        <v>-0.1369085173501577</v>
       </c>
       <c r="H3">
-        <v>0.1947791164658635</v>
+        <v>-0.1369085173501577</v>
       </c>
       <c r="I3">
-        <v>0.1044176706827309</v>
+        <v>0.2176656151419558</v>
       </c>
       <c r="J3">
-        <v>0.07300157150340492</v>
+        <v>0.1088328075709779</v>
       </c>
       <c r="K3">
-        <v>8.59</v>
+        <v>-0.022</v>
       </c>
       <c r="L3">
-        <v>0.05749665327978581</v>
+        <v>-0.003470031545741325</v>
       </c>
       <c r="M3">
-        <v>11.32</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.008869388074904019</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.317811408614668</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>9.65</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.007560918279401395</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.123399301513388</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1.67</v>
-      </c>
-      <c r="T3">
-        <v>0.1475265017667844</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>94.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.07396380161404059</v>
-      </c>
-      <c r="W3">
-        <v>0.09306608884073674</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.07266125985952787</v>
-      </c>
-      <c r="Y3">
-        <v>0.02040482898120886</v>
-      </c>
-      <c r="Z3">
-        <v>1.90561224489796</v>
-      </c>
-      <c r="AA3">
-        <v>0.1391126885536824</v>
+        <v>0.07120313264967332</v>
       </c>
       <c r="AB3">
-        <v>0.07246252407814478</v>
-      </c>
-      <c r="AC3">
-        <v>0.06665016447553758</v>
+        <v>0.0628183046331255</v>
       </c>
       <c r="AD3">
-        <v>9.460000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9.460000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="AG3">
-        <v>-84.94</v>
+        <v>3.15</v>
       </c>
       <c r="AH3">
-        <v>0.007357516177202589</v>
+        <v>0.3131212723658052</v>
       </c>
       <c r="AI3">
-        <v>0.05562742561448901</v>
+        <v>0.1611253196930947</v>
       </c>
       <c r="AJ3">
-        <v>-0.07129666935267258</v>
+        <v>0.3131212723658052</v>
       </c>
       <c r="AK3">
-        <v>-1.122653978324081</v>
+        <v>0.1611253196930947</v>
       </c>
       <c r="AL3">
-        <v>0.664</v>
+        <v>0.331</v>
       </c>
       <c r="AM3">
-        <v>-0.1739999999999999</v>
+        <v>0.331</v>
       </c>
       <c r="AN3">
-        <v>0.5058823529411766</v>
+        <v>2.157534246575342</v>
       </c>
       <c r="AO3">
-        <v>23.49397590361446</v>
+        <v>4.169184290030211</v>
       </c>
       <c r="AP3">
-        <v>-4.542245989304813</v>
+        <v>2.157534246575342</v>
       </c>
       <c r="AQ3">
-        <v>-89.65517241379314</v>
+        <v>4.169184290030211</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Forise International Limited (SGX:8A1)</t>
+          <t>iFAST Corporation Ltd. (SGX:AIY)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,104 +831,125 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.129</v>
+      </c>
+      <c r="E4">
+        <v>0.102</v>
+      </c>
+      <c r="F4">
+        <v>0.8909999999999999</v>
+      </c>
       <c r="G4">
-        <v>0.07565217391304348</v>
+        <v>0.1329044117647059</v>
       </c>
       <c r="H4">
-        <v>0.07565217391304348</v>
+        <v>0.09497549019607844</v>
       </c>
       <c r="I4">
-        <v>0.1808695652173913</v>
+        <v>0.116421568627451</v>
       </c>
       <c r="J4">
-        <v>0.1400538668718738</v>
+        <v>0.07928094550703718</v>
       </c>
       <c r="K4">
-        <v>-0.031</v>
+        <v>12</v>
       </c>
       <c r="L4">
-        <v>-0.02695652173913044</v>
+        <v>0.07352941176470588</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>11.019</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.00599249510550359</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.91825</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>10.4</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.005655862519034153</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.6189999999999998</v>
+      </c>
+      <c r="T4">
+        <v>0.05617569652418548</v>
       </c>
       <c r="U4">
-        <v>1.27</v>
+        <v>164.5</v>
       </c>
       <c r="V4">
-        <v>0.2360594795539034</v>
+        <v>0.08946051772895366</v>
       </c>
       <c r="W4">
-        <v>-0.01703296703296703</v>
+        <v>0.07712082262210797</v>
       </c>
       <c r="X4">
-        <v>0.07245421904070486</v>
+        <v>0.06262884821985559</v>
       </c>
       <c r="Y4">
-        <v>-0.08948718607367188</v>
+        <v>0.01449197440225237</v>
       </c>
       <c r="Z4">
-        <v>0.7958477508650518</v>
+        <v>2.309651853948486</v>
       </c>
       <c r="AA4">
-        <v>0.1114615549499341</v>
+        <v>0.1831113827731173</v>
       </c>
       <c r="AB4">
-        <v>0.07245421904070486</v>
+        <v>0.06229890718922979</v>
       </c>
       <c r="AC4">
-        <v>0.03900733590922929</v>
+        <v>0.1208124755838875</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="AG4">
-        <v>-1.27</v>
+        <v>-134.3</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.01615837346174425</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.1441527446300716</v>
       </c>
       <c r="AJ4">
-        <v>-0.3090024330900244</v>
+        <v>-0.07879143443825169</v>
       </c>
       <c r="AK4">
-        <v>-1.530120481927711</v>
+        <v>-2.984444444444445</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AM4">
-        <v>-0.004</v>
+        <v>3.092</v>
+      </c>
+      <c r="AN4">
+        <v>1.36036036036036</v>
+      </c>
+      <c r="AO4">
+        <v>5.688622754491019</v>
+      </c>
+      <c r="AP4">
+        <v>-6.049549549549551</v>
       </c>
       <c r="AQ4">
-        <v>-52</v>
+        <v>6.144890038809833</v>
       </c>
     </row>
     <row r="5">
@@ -972,43 +969,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0493</v>
+        <v>-0.103</v>
+      </c>
+      <c r="E5">
+        <v>0.189</v>
       </c>
       <c r="G5">
-        <v>0.2548476454293628</v>
+        <v>0.5007776049766719</v>
       </c>
       <c r="H5">
-        <v>0.2548476454293628</v>
+        <v>0.5007776049766719</v>
       </c>
       <c r="I5">
-        <v>0.2202216066481995</v>
+        <v>0.265940902021773</v>
       </c>
       <c r="J5">
-        <v>0.2113665420452124</v>
+        <v>0.2538600500701741</v>
       </c>
       <c r="K5">
-        <v>27.4</v>
+        <v>15.6</v>
       </c>
       <c r="L5">
-        <v>0.3795013850415512</v>
+        <v>0.2426127527216174</v>
       </c>
       <c r="M5">
-        <v>2.87</v>
+        <v>8.35</v>
       </c>
       <c r="N5">
-        <v>0.06119402985074628</v>
+        <v>0.1507220216606498</v>
       </c>
       <c r="O5">
-        <v>0.1047445255474453</v>
+        <v>0.5352564102564102</v>
       </c>
       <c r="P5">
-        <v>2.87</v>
+        <v>8.35</v>
       </c>
       <c r="Q5">
-        <v>0.06119402985074628</v>
+        <v>0.1507220216606498</v>
       </c>
       <c r="R5">
-        <v>0.1047445255474453</v>
+        <v>0.5352564102564102</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,73 +1017,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>45</v>
+        <v>31.5</v>
       </c>
       <c r="V5">
-        <v>0.9594882729211087</v>
+        <v>0.5685920577617328</v>
       </c>
       <c r="W5">
-        <v>0.2240392477514309</v>
+        <v>0.109704641350211</v>
       </c>
       <c r="X5">
-        <v>0.1195651026799244</v>
+        <v>0.08439142188944157</v>
       </c>
       <c r="Y5">
-        <v>0.1044741450715065</v>
+        <v>0.02531321946076941</v>
       </c>
       <c r="Z5">
-        <v>0.3782084861183866</v>
+        <v>0.3647192285876347</v>
       </c>
       <c r="AA5">
-        <v>0.0799406198829981</v>
+        <v>0.09258764163081223</v>
       </c>
       <c r="AB5">
-        <v>0.07316284377530519</v>
+        <v>0.0594357962377228</v>
       </c>
       <c r="AC5">
-        <v>0.006777776107692909</v>
+        <v>0.03315184539308944</v>
       </c>
       <c r="AD5">
-        <v>79.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>79.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="AG5">
-        <v>34.09999999999999</v>
+        <v>31.2</v>
       </c>
       <c r="AH5">
-        <v>0.6277777777777778</v>
+        <v>0.5309060118543608</v>
       </c>
       <c r="AI5">
-        <v>0.3566275924256087</v>
+        <v>0.2964539007092199</v>
       </c>
       <c r="AJ5">
-        <v>0.4209876543209876</v>
+        <v>0.3602771362586606</v>
       </c>
       <c r="AK5">
-        <v>0.1928733031674208</v>
+        <v>0.1733333333333333</v>
       </c>
       <c r="AL5">
-        <v>2.52</v>
+        <v>3.28</v>
       </c>
       <c r="AM5">
-        <v>2.52</v>
+        <v>3.28</v>
       </c>
       <c r="AN5">
-        <v>3.08984375</v>
+        <v>2.271739130434783</v>
       </c>
       <c r="AO5">
-        <v>6.309523809523809</v>
+        <v>5.213414634146342</v>
       </c>
       <c r="AP5">
-        <v>1.33203125</v>
+        <v>1.130434782608696</v>
       </c>
       <c r="AQ5">
-        <v>6.309523809523809</v>
+        <v>5.213414634146342</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TIH Limited (SGX:T55)</t>
+          <t>Yangzijiang Financial Holding Ltd. (SGX:YF8)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1102,122 +1102,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.11</v>
-      </c>
-      <c r="E6">
-        <v>-0.248</v>
+      <c r="F6">
+        <v>-0.014</v>
       </c>
       <c r="G6">
-        <v>1.462633451957295</v>
+        <v>0.8429447852760736</v>
       </c>
       <c r="H6">
-        <v>1.462633451957295</v>
+        <v>0.8429447852760736</v>
       </c>
       <c r="I6">
-        <v>0.3380782918149466</v>
+        <v>0.9002044989775051</v>
       </c>
       <c r="J6">
-        <v>0.2983043751308352</v>
+        <v>0.7013925188221592</v>
       </c>
       <c r="K6">
-        <v>1.5</v>
+        <v>139</v>
       </c>
       <c r="L6">
-        <v>0.2669039145907473</v>
+        <v>0.5685071574642127</v>
       </c>
       <c r="M6">
-        <v>1.74</v>
+        <v>121.4727</v>
       </c>
       <c r="N6">
-        <v>0.04317617866004963</v>
+        <v>0.1371178462580427</v>
       </c>
       <c r="O6">
-        <v>1.16</v>
+        <v>0.8739043165467626</v>
       </c>
       <c r="P6">
-        <v>1.74</v>
+        <v>46.7727</v>
       </c>
       <c r="Q6">
-        <v>0.04317617866004963</v>
+        <v>0.05279681679647816</v>
       </c>
       <c r="R6">
-        <v>1.16</v>
+        <v>0.3364942446043165</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>74.7</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.6149529894371328</v>
       </c>
       <c r="U6">
-        <v>7.29</v>
+        <v>396.4</v>
       </c>
       <c r="V6">
-        <v>0.180893300248139</v>
+        <v>0.4474545659781013</v>
       </c>
       <c r="W6">
-        <v>0.01597444089456869</v>
+        <v>0.04570413967711176</v>
       </c>
       <c r="X6">
-        <v>0.07252630420665011</v>
+        <v>0.06232407034784489</v>
       </c>
       <c r="Y6">
-        <v>-0.05655186331208142</v>
+        <v>-0.01661993067073313</v>
       </c>
       <c r="Z6">
-        <v>0.06736347509229515</v>
+        <v>0.08997971868181366</v>
       </c>
       <c r="AA6">
-        <v>0.02009481934404869</v>
+        <v>0.06311110152914658</v>
       </c>
       <c r="AB6">
-        <v>0.07244067407999208</v>
+        <v>0.06230404340617518</v>
       </c>
       <c r="AC6">
-        <v>-0.05234585473594339</v>
+        <v>0.0008070581229713963</v>
       </c>
       <c r="AD6">
-        <v>0.104</v>
+        <v>0.712</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.104</v>
+        <v>0.712</v>
       </c>
       <c r="AG6">
-        <v>-7.186</v>
+        <v>-395.688</v>
       </c>
       <c r="AH6">
-        <v>0.002574002574002574</v>
+        <v>0.0008030570305838405</v>
       </c>
       <c r="AI6">
-        <v>0.001147852191956205</v>
+        <v>0.0002508886815376939</v>
       </c>
       <c r="AJ6">
-        <v>-0.2170079120613638</v>
+        <v>-0.8071773028812024</v>
       </c>
       <c r="AK6">
-        <v>-0.08625201046642822</v>
+        <v>-0.1620667848448011</v>
       </c>
       <c r="AL6">
-        <v>0.308</v>
+        <v>0.604</v>
       </c>
       <c r="AM6">
-        <v>0.308</v>
+        <v>0.604</v>
       </c>
       <c r="AN6">
-        <v>0.05445026178010471</v>
+        <v>0.003217352010845006</v>
       </c>
       <c r="AO6">
-        <v>6.168831168831169</v>
+        <v>364.4039735099338</v>
       </c>
       <c r="AP6">
-        <v>-3.762303664921466</v>
+        <v>-1.788016267510167</v>
       </c>
       <c r="AQ6">
-        <v>6.168831168831169</v>
+        <v>364.4039735099338</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1225,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HHG Capital Corporation (NasdaqCM:HHGC)</t>
+          <t>TIH Limited (SGX:T55)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,88 +1234,97 @@
         </is>
       </c>
       <c r="K7">
-        <v>-0.162</v>
+        <v>-5.51</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>1.79</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.05233918128654971</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0.3248638838475499</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>1.79</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.05233918128654971</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0.3248638838475499</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>0.457</v>
+        <v>10.8</v>
       </c>
       <c r="V7">
-        <v>0.008908382066276805</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="W7">
-        <v>-0.015</v>
+        <v>-0.06088397790055249</v>
       </c>
       <c r="X7">
-        <v>0.07251955939580143</v>
+        <v>0.06250750183718075</v>
       </c>
       <c r="Y7">
-        <v>-0.08751955939580143</v>
+        <v>-0.1233914797377332</v>
       </c>
       <c r="Z7">
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>-0.04704112337011033</v>
+        <v>-0.06817581678949516</v>
       </c>
       <c r="AB7">
-        <v>0.07246421386628965</v>
+        <v>0.0622537314724473</v>
       </c>
       <c r="AC7">
-        <v>-0.1195053372364</v>
+        <v>-0.1304295482619425</v>
       </c>
       <c r="AD7">
-        <v>0.12</v>
+        <v>0.349</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.12</v>
+        <v>0.349</v>
       </c>
       <c r="AG7">
-        <v>-0.337</v>
+        <v>-10.451</v>
       </c>
       <c r="AH7">
-        <v>0.002333722287047842</v>
+        <v>0.01010159483631943</v>
       </c>
       <c r="AI7">
-        <v>-0.103448275862069</v>
+        <v>0.004051120732684071</v>
       </c>
       <c r="AJ7">
-        <v>-0.006612640543139142</v>
+        <v>-0.4400606341319634</v>
       </c>
       <c r="AK7">
-        <v>0.2084106369820656</v>
+        <v>-0.1387012435466961</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.307</v>
+        <v>-0.5669999999999999</v>
+      </c>
+      <c r="AN7">
+        <v>-0.06176991150442477</v>
+      </c>
+      <c r="AP7">
+        <v>1.849734513274336</v>
       </c>
       <c r="AQ7">
-        <v>1.527687296416938</v>
+        <v>10.01763668430335</v>
       </c>
     </row>
     <row r="8">
@@ -1329,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nova Vision Acquisition Corporation (NasdaqCM:NOVV)</t>
+          <t>A SPAC I Acquisition Corp. (NasdaqCM:ASCA)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1338,7 +1344,7 @@
         </is>
       </c>
       <c r="K8">
-        <v>-0.446</v>
+        <v>0.739</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1347,7 +1353,7 @@
         <v>-0</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1356,70 +1362,70 @@
         <v>-0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.227</v>
+        <v>0.039</v>
       </c>
       <c r="V8">
-        <v>0.0060857908847185</v>
+        <v>0.0009605911330049261</v>
       </c>
       <c r="W8">
-        <v>-0.0892</v>
+        <v>0.191948051948052</v>
       </c>
       <c r="X8">
-        <v>0.07289156148181505</v>
+        <v>0.06299082663255769</v>
       </c>
       <c r="Y8">
-        <v>-0.1620915614818151</v>
+        <v>0.1289572253154943</v>
       </c>
       <c r="Z8">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>-0.1894262683736368</v>
+        <v>-0.3641679957469431</v>
       </c>
       <c r="AB8">
-        <v>0.07237309944228966</v>
+        <v>0.06236342093483679</v>
       </c>
       <c r="AC8">
-        <v>-0.2617993678159264</v>
+        <v>-0.42653141668178</v>
       </c>
       <c r="AD8">
-        <v>0.584</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.584</v>
+        <v>1.42</v>
       </c>
       <c r="AG8">
-        <v>0.357</v>
+        <v>1.381</v>
       </c>
       <c r="AH8">
-        <v>0.01541547883011297</v>
+        <v>0.03379343169919086</v>
       </c>
       <c r="AI8">
-        <v>-1.280701754385965</v>
+        <v>-0.484641638225256</v>
       </c>
       <c r="AJ8">
-        <v>0.00948030910587673</v>
+        <v>0.03289583382958958</v>
       </c>
       <c r="AK8">
-        <v>-0.5226939970717422</v>
+        <v>-0.4651397777029304</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-0.353</v>
+        <v>-2.11</v>
       </c>
       <c r="AQ8">
-        <v>2.263456090651558</v>
+        <v>0.6492890995260664</v>
       </c>
     </row>
     <row r="9">
@@ -1430,7 +1436,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A SPAC II Acquisition Corporation (NasdaqGM:ASCB)</t>
+          <t>Forise International Limited (SGX:8A1)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1438,8 +1444,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>-0.455</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>-12.53968253968254</v>
+      </c>
+      <c r="J9">
+        <v>-12.53968253968254</v>
+      </c>
       <c r="K9">
-        <v>-0.006</v>
+        <v>-1.2</v>
+      </c>
+      <c r="L9">
+        <v>-9.523809523809524</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1463,31 +1487,31 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>1.12</v>
+        <v>0.655</v>
       </c>
       <c r="V9">
-        <v>0.004327666151468315</v>
+        <v>0.1915204678362573</v>
       </c>
       <c r="W9">
-        <v>-0.2727272727272728</v>
+        <v>-0.689655172413793</v>
       </c>
       <c r="X9">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y9">
-        <v>-0.3451814917679776</v>
+        <v>-0.7519635609495947</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>0.2680851063829787</v>
       </c>
       <c r="AA9">
-        <v>-0.24</v>
+        <v>-3.361702127659575</v>
       </c>
       <c r="AB9">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC9">
-        <v>-0.3124542190407049</v>
+        <v>-3.424010516195376</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -1499,25 +1523,28 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>-1.12</v>
+        <v>-0.655</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AI9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>-0.004346476249611922</v>
+        <v>-0.2368896925858952</v>
       </c>
       <c r="AK9">
-        <v>0.163265306122449</v>
+        <v>3.429319371727749</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>-0.004</v>
+      </c>
+      <c r="AQ9">
+        <v>395</v>
       </c>
     </row>
     <row r="10">
@@ -1528,7 +1555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A SPAC I Acquisition Corp. (NasdaqCM:ASCA)</t>
+          <t>Chenghe Acquisition I Co. (NasdaqGM:LATG)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1537,16 +1564,16 @@
         </is>
       </c>
       <c r="K10">
-        <v>0.025</v>
+        <v>4.43</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>7.9</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.08094262295081968</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>1.783295711060948</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1558,34 +1585,37 @@
         <v>-0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>7.9</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>0.08799999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="V10">
-        <v>0.000992108229988726</v>
+        <v>0.009579918032786886</v>
       </c>
       <c r="W10">
-        <v>1.086956521739131</v>
+        <v>-67.12121212121211</v>
       </c>
       <c r="X10">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y10">
-        <v>1.014502302698426</v>
+        <v>-67.18352050974791</v>
       </c>
       <c r="Z10">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>-1.777272727272727</v>
+        <v>-40.55555555555556</v>
       </c>
       <c r="AB10">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC10">
-        <v>-1.849726946313432</v>
+        <v>-40.61786394409137</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -1597,28 +1627,28 @@
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>-0.08799999999999999</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10">
-        <v>-0.0009930934862095425</v>
+        <v>-0.009672580561733824</v>
       </c>
       <c r="AK10">
-        <v>-0.02339181286549707</v>
+        <v>0.1541632316570486</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-0.416</v>
+        <v>-3.33</v>
       </c>
       <c r="AQ10">
-        <v>0.9399038461538463</v>
+        <v>0.4384384384384384</v>
       </c>
     </row>
     <row r="11">
@@ -1629,7 +1659,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chenghe Acquisition Co. (NasdaqGM:CHEA)</t>
+          <t>L Catterton Asia Acquisition Corp (NasdaqCM:LCAA)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1638,16 +1668,16 @@
         </is>
       </c>
       <c r="K11">
-        <v>0.206</v>
+        <v>0.804</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>70.2</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.225</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>87.31343283582089</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1659,34 +1689,28 @@
         <v>-0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>70.2</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>0.672</v>
+        <v>0.005</v>
       </c>
       <c r="V11">
-        <v>0.004537474679270763</v>
+        <v>1.602564102564103e-05</v>
       </c>
       <c r="W11">
-        <v>12.875</v>
+        <v>-0.06137404580152672</v>
       </c>
       <c r="X11">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y11">
-        <v>12.80254578095929</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>-2.842105263157894</v>
+        <v>-0.1236824343373284</v>
       </c>
       <c r="AB11">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AC11">
-        <v>-2.914559482198599</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -1698,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>-0.672</v>
+        <v>-0.005</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1707,19 +1731,19 @@
         <v>-0</v>
       </c>
       <c r="AJ11">
-        <v>-0.004558157202159699</v>
+        <v>-1.60258978509271e-05</v>
       </c>
       <c r="AK11">
-        <v>0.1674975074775673</v>
+        <v>0.0002136295663319804</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-0.655</v>
+        <v>-10.7</v>
       </c>
       <c r="AQ11">
-        <v>0.6595419847328244</v>
+        <v>0.5644859813084112</v>
       </c>
     </row>
     <row r="12">
@@ -1730,7 +1754,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fat Projects Acquisition Corp (NasdaqGM:FATP)</t>
+          <t>AP Acquisition Corp. (NYSE:APCA)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1739,7 +1763,7 @@
         </is>
       </c>
       <c r="K12">
-        <v>-1.21</v>
+        <v>3.8</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1748,7 +1772,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1757,70 +1781,61 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0.244</v>
+        <v>0.142</v>
       </c>
       <c r="V12">
-        <v>0.001660993873383254</v>
+        <v>0.0008170310701956271</v>
       </c>
       <c r="W12">
-        <v>48.4</v>
+        <v>-0.6654991243432574</v>
       </c>
       <c r="X12">
-        <v>0.07245421904070486</v>
+        <v>0.06254302605935201</v>
       </c>
       <c r="Y12">
-        <v>48.32754578095929</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>-17.71929824561403</v>
+        <v>-0.7280421504026094</v>
       </c>
       <c r="AB12">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AC12">
-        <v>-17.79175246465474</v>
+        <v>0.06232773899548229</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG12">
-        <v>-0.244</v>
+        <v>1.948</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.01188242651657286</v>
       </c>
       <c r="AI12">
-        <v>-0</v>
+        <v>-0.2244897959183673</v>
       </c>
       <c r="AJ12">
-        <v>-0.00166375736417194</v>
+        <v>0.01108405216560075</v>
       </c>
       <c r="AK12">
-        <v>0.04847040127135479</v>
+        <v>-0.2060939483707152</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-0.8090000000000001</v>
+        <v>-7.98</v>
       </c>
       <c r="AQ12">
-        <v>2.496909765142151</v>
+        <v>0.525062656641604</v>
       </c>
     </row>
     <row r="13">
@@ -1831,7 +1846,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RF Acquisition Corp. (NasdaqGM:RFAC)</t>
+          <t>Novo Tellus Alpha Acquisition (SGX:NTA)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1840,16 +1855,16 @@
         </is>
       </c>
       <c r="K13">
-        <v>-0.155</v>
+        <v>2.62</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>22.9</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.1588072122052705</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>8.740458015267174</v>
       </c>
       <c r="P13">
         <v>-0</v>
@@ -1858,37 +1873,25 @@
         <v>-0</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>22.9</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>0.285</v>
+        <v>0.583</v>
       </c>
       <c r="V13">
-        <v>0.001933514246947082</v>
-      </c>
-      <c r="W13">
-        <v>-8.157894736842106</v>
+        <v>0.004042995839112344</v>
       </c>
       <c r="X13">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="Y13">
-        <v>-8.23034895588281</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>-38.78947368421053</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB13">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AC13">
-        <v>-38.86192790325124</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -1900,28 +1903,28 @@
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>-0.285</v>
+        <v>-0.583</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13">
-        <v>-0.001937259966692723</v>
+        <v>-0.004059408008801187</v>
       </c>
       <c r="AK13">
-        <v>2.209302325581396</v>
+        <v>0.3215664644236073</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-0.697</v>
+        <v>-3.36</v>
       </c>
       <c r="AQ13">
-        <v>1.057388809182209</v>
+        <v>0.1595238095238095</v>
       </c>
     </row>
     <row r="14">
@@ -1932,7 +1935,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Catcha Investment Corp (NYSE:CHAA)</t>
+          <t>Pegasus Asia (SGX:PGS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1941,16 +1944,16 @@
         </is>
       </c>
       <c r="K14">
-        <v>10.1</v>
+        <v>-4.55</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>26.3</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.1849507735583685</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>-5.780219780219781</v>
       </c>
       <c r="P14">
         <v>-0</v>
@@ -1959,61 +1962,58 @@
         <v>-0</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>26.3</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>0.076</v>
+        <v>0.027</v>
       </c>
       <c r="V14">
-        <v>0.000200845665961945</v>
-      </c>
-      <c r="W14">
-        <v>-0.5179487179487179</v>
+        <v>0.000189873417721519</v>
       </c>
       <c r="X14">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="Y14">
-        <v>-0.5904029369894227</v>
+        <v>0.06231717029106902</v>
       </c>
       <c r="AB14">
-        <v>0.07245421904070486</v>
+        <v>0.06230912114287532</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AG14">
-        <v>-0.076</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.0004498678513186752</v>
       </c>
       <c r="AI14">
-        <v>-0</v>
+        <v>0.003339595074097266</v>
       </c>
       <c r="AJ14">
-        <v>-0.0002008860130470179</v>
+        <v>0.0002601292209481359</v>
       </c>
       <c r="AK14">
-        <v>0.00662251655629139</v>
+        <v>0.001933427391963213</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1.63</v>
+        <v>-3.11</v>
       </c>
       <c r="AQ14">
-        <v>0.7914110429447854</v>
+        <v>2.553054662379421</v>
       </c>
     </row>
     <row r="15">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L Catterton Asia Acquisition Corp (NasdaqCM:LCAA)</t>
+          <t>Chenghe Acquisition Co. (NasdaqGM:CHEA)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2033,16 +2033,16 @@
         </is>
       </c>
       <c r="K15">
-        <v>7.96</v>
+        <v>2.46</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>32.8</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.2636655948553054</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2054,58 +2054,61 @@
         <v>-0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>32.8</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
       </c>
       <c r="U15">
-        <v>0.067</v>
+        <v>0.186</v>
       </c>
       <c r="V15">
-        <v>0.0001852363837434338</v>
+        <v>0.001495176848874598</v>
       </c>
       <c r="W15">
-        <v>-0.4124352331606218</v>
+        <v>-0.7365269461077845</v>
       </c>
       <c r="X15">
-        <v>0.07245421904070486</v>
+        <v>0.06232407339310446</v>
       </c>
       <c r="Y15">
-        <v>-0.4848894522013266</v>
+        <v>-0.7988510195008889</v>
       </c>
       <c r="AB15">
-        <v>0.07245421904070486</v>
+        <v>0.06230969656306984</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG15">
-        <v>-0.067</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>0.0008032128514056225</v>
       </c>
       <c r="AI15">
-        <v>-0</v>
+        <v>-0.01706484641638225</v>
       </c>
       <c r="AJ15">
-        <v>-0.0001852707026184004</v>
+        <v>-0.0006917965796290039</v>
       </c>
       <c r="AK15">
-        <v>0.005088478772689299</v>
+        <v>0.01422428051604366</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1.72</v>
+        <v>-4.89</v>
       </c>
       <c r="AQ15">
-        <v>2.13953488372093</v>
+        <v>0.4948875255623722</v>
       </c>
     </row>
     <row r="16">
@@ -2116,7 +2119,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ZACD Group Ltd. (SEHK:8313)</t>
+          <t>Catcha Investment Corp (NYSEAM:CHAA)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2124,35 +2127,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D16">
-        <v>-0.18</v>
-      </c>
-      <c r="G16">
-        <v>1.36968085106383</v>
-      </c>
-      <c r="H16">
-        <v>1.36968085106383</v>
-      </c>
-      <c r="I16">
-        <v>-0.1816489361702128</v>
-      </c>
-      <c r="J16">
-        <v>-0.1816489361702128</v>
-      </c>
       <c r="K16">
-        <v>-0.216</v>
-      </c>
-      <c r="L16">
-        <v>-0.0574468085106383</v>
+        <v>-2.42</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>282.9</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>2.617021276595745</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>-116.900826446281</v>
       </c>
       <c r="P16">
         <v>-0</v>
@@ -2164,61 +2149,533 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>282.9</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>7.400555041628123e-05</v>
+      </c>
+      <c r="W16">
+        <v>0.212280701754386</v>
       </c>
       <c r="X16">
-        <v>0.07564409887632229</v>
+        <v>0.06274339158472082</v>
+      </c>
+      <c r="Y16">
+        <v>0.1495373101696651</v>
       </c>
       <c r="AB16">
-        <v>0.07289317461476016</v>
+        <v>0.06234390270118832</v>
       </c>
       <c r="AD16">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="AG16">
-        <v>1.85</v>
+        <v>2.402</v>
       </c>
       <c r="AH16">
-        <v>0.1024930747922438</v>
+        <v>0.02180798117817392</v>
       </c>
       <c r="AI16">
-        <v>0.1024930747922438</v>
+        <v>-0.3937908496732027</v>
       </c>
       <c r="AJ16">
-        <v>0.1024930747922438</v>
+        <v>0.02173716312826917</v>
       </c>
       <c r="AK16">
-        <v>0.1024930747922438</v>
+        <v>-0.3919712793733682</v>
       </c>
       <c r="AL16">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>0.062</v>
-      </c>
-      <c r="AN16">
-        <v>-2.732644017725258</v>
-      </c>
-      <c r="AO16">
-        <v>-11.01612903225807</v>
-      </c>
-      <c r="AP16">
-        <v>-2.732644017725258</v>
+        <v>-4.89</v>
       </c>
       <c r="AQ16">
-        <v>-11.01612903225807</v>
+        <v>1.261758691206544</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A SPAC II Acquisition Corporation (NasdaqGM:ASCB)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K17">
+        <v>6.86</v>
+      </c>
+      <c r="M17">
+        <v>190.7</v>
+      </c>
+      <c r="N17">
+        <v>2.407828282828282</v>
+      </c>
+      <c r="O17">
+        <v>27.79883381924198</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>-0</v>
+      </c>
+      <c r="S17">
+        <v>190.7</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>0.532</v>
+      </c>
+      <c r="V17">
+        <v>0.006717171717171717</v>
+      </c>
+      <c r="W17">
+        <v>-1.195121951219512</v>
+      </c>
+      <c r="X17">
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="Y17">
+        <v>-1.257430339755314</v>
+      </c>
+      <c r="AB17">
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>-0.532</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>-0</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.006762597244114506</v>
+      </c>
+      <c r="AK17">
+        <v>0.07501410039481106</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-7.71</v>
+      </c>
+      <c r="AQ17">
+        <v>0.1108949416342412</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RF Acquisition Corp. (NasdaqGM:RFAC)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K18">
+        <v>0.33</v>
+      </c>
+      <c r="M18">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="N18">
+        <v>1.051880674448768</v>
+      </c>
+      <c r="O18">
+        <v>245.7575757575757</v>
+      </c>
+      <c r="P18">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>-0</v>
+      </c>
+      <c r="R18">
+        <v>-0</v>
+      </c>
+      <c r="S18">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>0.004</v>
+      </c>
+      <c r="V18">
+        <v>5.188067444876784e-05</v>
+      </c>
+      <c r="W18">
+        <v>2.115384615384615</v>
+      </c>
+      <c r="X18">
+        <v>0.06250907577640319</v>
+      </c>
+      <c r="Y18">
+        <v>2.052875539608212</v>
+      </c>
+      <c r="AB18">
+        <v>0.06232496763407092</v>
+      </c>
+      <c r="AD18">
+        <v>0.793</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0.793</v>
+      </c>
+      <c r="AG18">
+        <v>0.789</v>
+      </c>
+      <c r="AH18">
+        <v>0.01018063240599284</v>
+      </c>
+      <c r="AI18">
+        <v>-0.3163143199042681</v>
+      </c>
+      <c r="AJ18">
+        <v>0.01012980010014251</v>
+      </c>
+      <c r="AK18">
+        <v>-0.3142174432497014</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-3.16</v>
+      </c>
+      <c r="AQ18">
+        <v>0.6962025316455697</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aura FAT Projects Acquisition Corp (NasdaqGM:AFAR)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K19">
+        <v>3.03</v>
+      </c>
+      <c r="M19">
+        <v>92.5</v>
+      </c>
+      <c r="N19">
+        <v>1.472929936305733</v>
+      </c>
+      <c r="O19">
+        <v>30.52805280528053</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>-0</v>
+      </c>
+      <c r="S19">
+        <v>92.5</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>0.045</v>
+      </c>
+      <c r="V19">
+        <v>0.0007165605095541402</v>
+      </c>
+      <c r="W19">
+        <v>-0.8859649122807017</v>
+      </c>
+      <c r="X19">
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="Y19">
+        <v>-0.9482733008165034</v>
+      </c>
+      <c r="AB19">
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>-0.045</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>-0</v>
+      </c>
+      <c r="AJ19">
+        <v>-0.0007170743367062386</v>
+      </c>
+      <c r="AK19">
+        <v>0.008746355685131196</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-4.6</v>
+      </c>
+      <c r="AQ19">
+        <v>0.3434782608695652</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HHG Capital Corporation (NasdaqCM:HHGC)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K20">
+        <v>0.998</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>-0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>-0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0.007</v>
+      </c>
+      <c r="V20">
+        <v>0.0001245551601423488</v>
+      </c>
+      <c r="W20">
+        <v>-0.7796875</v>
+      </c>
+      <c r="X20">
+        <v>0.06232227605358435</v>
+      </c>
+      <c r="Y20">
+        <v>-0.8420097760535843</v>
+      </c>
+      <c r="AB20">
+        <v>0.06230954678185349</v>
+      </c>
+      <c r="AD20">
+        <v>0.04</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0.04</v>
+      </c>
+      <c r="AG20">
+        <v>0.033</v>
+      </c>
+      <c r="AH20">
+        <v>0.0007112375533428165</v>
+      </c>
+      <c r="AI20">
+        <v>-0.02285714285714286</v>
+      </c>
+      <c r="AJ20">
+        <v>0.0005868440239716892</v>
+      </c>
+      <c r="AK20">
+        <v>-0.01878201479795105</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1.4</v>
+      </c>
+      <c r="AQ20">
+        <v>0.4392857142857143</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nova Vision Acquisition Corporation (NasdaqCM:NOVV)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K21">
+        <v>0.217</v>
+      </c>
+      <c r="M21">
+        <v>43.4</v>
+      </c>
+      <c r="N21">
+        <v>1.142105263157895</v>
+      </c>
+      <c r="O21">
+        <v>200</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>-0</v>
+      </c>
+      <c r="S21">
+        <v>43.4</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>0.163</v>
+      </c>
+      <c r="V21">
+        <v>0.004289473684210526</v>
+      </c>
+      <c r="W21">
+        <v>-0.2086538461538461</v>
+      </c>
+      <c r="X21">
+        <v>0.06333533392973402</v>
+      </c>
+      <c r="Y21">
+        <v>-0.2719891800835801</v>
+      </c>
+      <c r="AB21">
+        <v>0.06203785173324732</v>
+      </c>
+      <c r="AD21">
+        <v>2</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>2</v>
+      </c>
+      <c r="AG21">
+        <v>1.837</v>
+      </c>
+      <c r="AH21">
+        <v>0.05</v>
+      </c>
+      <c r="AI21">
+        <v>-3.389830508474577</v>
+      </c>
+      <c r="AJ21">
+        <v>0.04611291010869292</v>
+      </c>
+      <c r="AK21">
+        <v>-2.439575033200532</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-0.951</v>
+      </c>
+      <c r="AQ21">
+        <v>0.7718191377497371</v>
       </c>
     </row>
   </sheetData>
